--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 17,29</t>
+          <t>-5,63; 17,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 18,11</t>
+          <t>-6,53; 18,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 4,09</t>
+          <t>-15,42; 5,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 10,62</t>
+          <t>-7,57; 11,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 13,26</t>
+          <t>-8,19; 15,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 26,93</t>
+          <t>0,96; 26,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,99</t>
+          <t>-3,47; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 11,61</t>
+          <t>-4,29; 12,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 14,39</t>
+          <t>-2,73; 15,63</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 211,64</t>
+          <t>-32,62; 240,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 210,09</t>
+          <t>-37,23; 211,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,44; 62,82</t>
+          <t>-79,55; 77,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 154,95</t>
+          <t>-46,82; 160,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 176,19</t>
+          <t>-50,31; 205,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 339,41</t>
+          <t>2,72; 343,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 117,78</t>
+          <t>-22,7; 128,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 120,38</t>
+          <t>-28,55; 129,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 139,49</t>
+          <t>-18,6; 169,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,27</t>
+          <t>-0,21; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,83</t>
+          <t>-1,4; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,73</t>
+          <t>-3,23; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 5,88</t>
+          <t>-0,96; 6,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,52</t>
+          <t>-3,68; 2,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,54</t>
+          <t>-2,87; 3,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,3</t>
+          <t>0,43; 5,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,52</t>
+          <t>-1,84; 2,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,25</t>
+          <t>-2,1; 2,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 163,84</t>
+          <t>-3,55; 147,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 110,04</t>
+          <t>-19,58; 113,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 62,84</t>
+          <t>-39,91; 61,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 94,61</t>
+          <t>-11,35; 102,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 44,94</t>
+          <t>-40,2; 44,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 57,66</t>
+          <t>-32,08; 63,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 90,59</t>
+          <t>3,81; 86,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 42,86</t>
+          <t>-23,24; 46,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 39,24</t>
+          <t>-26,23; 41,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,11</t>
+          <t>-2,3; 7,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 7,75</t>
+          <t>-2,17; 7,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,89</t>
+          <t>-3,79; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 2,8</t>
+          <t>-6,99; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -0,39</t>
+          <t>-9,38; -0,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,29</t>
+          <t>-8,7; -0,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 4,15</t>
+          <t>-3,24; 3,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,15</t>
+          <t>-4,16; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 1,16</t>
+          <t>-5,12; 0,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 300,6</t>
+          <t>-44,5; 312,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 347,47</t>
+          <t>-35,86; 288,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 183,07</t>
+          <t>-58,39; 216,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 74,94</t>
+          <t>-70,6; 88,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 6,04</t>
+          <t>-87,39; 2,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 5,14</t>
+          <t>-85,65; 2,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 93,16</t>
+          <t>-45,51; 104,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 54,67</t>
+          <t>-54,56; 56,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,96; 31,06</t>
+          <t>-66,46; 30,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,41</t>
+          <t>0,75; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,66</t>
+          <t>-1,0; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,82</t>
+          <t>-3,05; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,07</t>
+          <t>-1,63; 4,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,15</t>
+          <t>-4,03; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,01</t>
+          <t>-2,51; 2,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,26</t>
+          <t>0,36; 4,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,02</t>
+          <t>-1,62; 2,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,84</t>
+          <t>-1,91; 1,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 118,21</t>
+          <t>8,41; 121,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 85,52</t>
+          <t>-13,27; 86,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 35,18</t>
+          <t>-39,05; 37,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 58,71</t>
+          <t>-17,65; 61,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 18,43</t>
+          <t>-43,07; 18,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 44,99</t>
+          <t>-26,87; 42,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,12; 67,99</t>
+          <t>4,03; 71,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 33,18</t>
+          <t>-20,48; 31,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 29,35</t>
+          <t>-22,43; 26,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 17,98</t>
+          <t>-5,82; 17,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 18,32</t>
+          <t>-5,98; 17,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 5,45</t>
+          <t>-15,52; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 11,43</t>
+          <t>-8,82; 11,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 15,34</t>
+          <t>-8,26; 15,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 26,68</t>
+          <t>0,69; 26,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 10,98</t>
+          <t>-5,06; 10,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 12,51</t>
+          <t>-4,66; 11,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 15,63</t>
+          <t>-3,29; 13,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 240,06</t>
+          <t>-31,63; 222,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 211,9</t>
+          <t>-38,03; 216,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 77,54</t>
+          <t>-82,08; 58,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 160,14</t>
+          <t>-49,61; 167,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 205,65</t>
+          <t>-48,64; 207,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 343,12</t>
+          <t>-1,25; 328,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 128,85</t>
+          <t>-30,18; 116,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 129,54</t>
+          <t>-27,09; 129,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 169,32</t>
+          <t>-22,74; 154,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 7,06</t>
+          <t>0,1; 7,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,08</t>
+          <t>-1,36; 4,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,81</t>
+          <t>-3,22; 2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,16</t>
+          <t>-1,22; 5,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,52</t>
+          <t>-3,76; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,64</t>
+          <t>-2,93; 3,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,17</t>
+          <t>0,31; 5,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,69</t>
+          <t>-1,7; 2,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,3</t>
+          <t>-2,08; 2,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 147,83</t>
+          <t>-0,82; 164,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 113,67</t>
+          <t>-19,45; 104,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 61,7</t>
+          <t>-42,1; 56,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 102,07</t>
+          <t>-15,35; 97,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 44,23</t>
+          <t>-41,23; 44,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 63,21</t>
+          <t>-32,72; 57,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 86,81</t>
+          <t>3,68; 91,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 46,7</t>
+          <t>-21,57; 49,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 41,44</t>
+          <t>-26,02; 37,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 7,98</t>
+          <t>-2,13; 8,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,4</t>
+          <t>-1,63; 7,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,24</t>
+          <t>-3,68; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,23</t>
+          <t>-6,99; 3,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,57</t>
+          <t>-9,16; -0,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -0,06</t>
+          <t>-8,96; -0,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,95</t>
+          <t>-3,57; 3,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,06</t>
+          <t>-4,58; 1,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,97</t>
+          <t>-5,01; 0,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 312,65</t>
+          <t>-41,6; 354,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 288,44</t>
+          <t>-29,7; 281,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 216,6</t>
+          <t>-59,92; 211,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,6; 88,39</t>
+          <t>-70,64; 83,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 2,59</t>
+          <t>-89,47; 10,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,65; 2,3</t>
+          <t>-84,15; 19,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 104,83</t>
+          <t>-48,14; 87,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 56,98</t>
+          <t>-60,05; 46,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 30,12</t>
+          <t>-65,71; 26,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,63</t>
+          <t>0,79; 6,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,65</t>
+          <t>-0,64; 4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,91</t>
+          <t>-3,06; 1,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,02</t>
+          <t>-1,56; 3,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,12</t>
+          <t>-4,03; 1,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,77</t>
+          <t>-2,49; 3,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,44</t>
+          <t>0,35; 4,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,07</t>
+          <t>-1,8; 1,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,61</t>
+          <t>-1,96; 1,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 121,93</t>
+          <t>9,1; 128,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 86,89</t>
+          <t>-10,37; 95,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 37,89</t>
+          <t>-39,7; 31,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 61,61</t>
+          <t>-17,05; 56,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 18,13</t>
+          <t>-42,73; 18,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 42,87</t>
+          <t>-27,34; 46,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 71,64</t>
+          <t>3,38; 67,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 31,94</t>
+          <t>-22,45; 28,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 26,17</t>
+          <t>-23,45; 25,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,73</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>6,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 17,86</t>
+          <t>-8,68; 10,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 17,67</t>
+          <t>-8,91; 13,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 4,77</t>
+          <t>0,27; 25,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 11,71</t>
+          <t>-6,95; 17,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 15,91</t>
+          <t>-7,62; 18,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 26,3</t>
+          <t>-13,76; 9,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 10,81</t>
+          <t>-3,95; 10,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 11,99</t>
+          <t>-4,13; 11,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 13,7</t>
+          <t>-1,75; 15,85</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>101,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>39,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>37,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-39,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110,4%</t>
+          <t>-15,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 222,66</t>
+          <t>-50,17; 154,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 216,71</t>
+          <t>-51,31; 176,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 58,73</t>
+          <t>-3,28; 327,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 167,28</t>
+          <t>-38,46; 211,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 207,33</t>
+          <t>-41,13; 210,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 328,82</t>
+          <t>-71,49; 110,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 116,62</t>
+          <t>-24,48; 117,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 129,3</t>
+          <t>-25,18; 120,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 154,33</t>
+          <t>-12,97; 156,54</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,2</t>
+          <t>-1,58; 5,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,67</t>
+          <t>-3,79; 2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,51</t>
+          <t>-3,12; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,87</t>
+          <t>0,23; 7,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,59</t>
+          <t>-1,52; 4,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,32</t>
+          <t>-3,03; 3,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,43</t>
+          <t>0,53; 5,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,79</t>
+          <t>-1,87; 2,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,21</t>
+          <t>-2,1; 2,29</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-8,65%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>58,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>28,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,36%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,65%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 164,41</t>
+          <t>-18,77; 94,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 104,62</t>
+          <t>-42,2; 44,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 56,66</t>
+          <t>-34,61; 55,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 97,54</t>
+          <t>2,38; 163,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 44,1</t>
+          <t>-21,58; 110,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 57,85</t>
+          <t>-38,08; 68,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 91,74</t>
+          <t>4,82; 90,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 49,67</t>
+          <t>-23,87; 42,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 37,68</t>
+          <t>-25,37; 40,59</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,03</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,61</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-2,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 8,09</t>
+          <t>-7,79; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 7,02</t>
+          <t>-9,4; -0,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,17</t>
+          <t>-9,52; -0,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,27</t>
+          <t>-2,06; 8,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -0,45</t>
+          <t>-1,94; 7,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -0,18</t>
+          <t>-3,93; 4,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,6</t>
+          <t>-3,1; 4,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,89</t>
+          <t>-3,99; 2,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,93</t>
+          <t>-5,35; 0,68</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-27,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-63,75%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-64,24%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>54,02%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>54,39%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-27,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-63,75%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-58,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-33,75%</t>
+          <t>-38,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 354,91</t>
+          <t>-72,74; 74,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 281,66</t>
+          <t>-89,18; 6,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 211,21</t>
+          <t>-87,38; -4,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 83,49</t>
+          <t>-36,94; 300,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-89,47; 10,4</t>
+          <t>-36,61; 347,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,15; 19,25</t>
+          <t>-61,11; 177,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,14; 87,32</t>
+          <t>-42,93; 93,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 46,99</t>
+          <t>-55,0; 54,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 26,78</t>
+          <t>-65,8; 21,55</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,62</t>
+          <t>-1,78; 4,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,84</t>
+          <t>-3,93; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,65</t>
+          <t>-2,67; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,88</t>
+          <t>0,45; 6,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,21</t>
+          <t>-0,95; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,16</t>
+          <t>-2,56; 2,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,35</t>
+          <t>0,3; 4,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,88</t>
+          <t>-1,49; 2,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,62</t>
+          <t>-1,78; 1,8</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-17,02%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,51%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>54,91%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-8,79%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-2,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,1; 128,79</t>
+          <t>-20,85; 58,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 95,68</t>
+          <t>-41,85; 18,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 31,33</t>
+          <t>-29,43; 40,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 56,53</t>
+          <t>3,02; 118,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 18,61</t>
+          <t>-12,62; 85,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 46,24</t>
+          <t>-32,11; 43,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 67,98</t>
+          <t>4,12; 67,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 28,57</t>
+          <t>-18,8; 33,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 25,24</t>
+          <t>-22,0; 28,71</t>
         </is>
       </c>
     </row>
